--- a/backend/data/financials_by_company/0910.HK.xlsx
+++ b/backend/data/financials_by_company/0910.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,611 +672,665 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-97865460.211319</v>
+        <v>33121000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.162392</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-3833694000</v>
+        <v>449874000</v>
       </c>
       <c r="E2" t="n">
-        <v>-602648000</v>
+        <v>132484000</v>
       </c>
       <c r="F2" t="n">
-        <v>-602648000</v>
+        <v>132484000</v>
       </c>
       <c r="G2" t="n">
-        <v>-4051720000</v>
+        <v>169707000</v>
       </c>
       <c r="H2" t="n">
-        <v>1217000</v>
+        <v>20498000</v>
       </c>
       <c r="I2" t="n">
-        <v>1941649000</v>
+        <v>2113085000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4436342000</v>
+        <v>582358000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4437559000</v>
+        <v>561860000</v>
       </c>
       <c r="L2" t="n">
-        <v>-402980000</v>
+        <v>-174671000</v>
       </c>
       <c r="M2" t="n">
-        <v>403554000</v>
+        <v>178165000</v>
       </c>
       <c r="N2" t="n">
-        <v>574000</v>
+        <v>3494000</v>
       </c>
       <c r="O2" t="n">
-        <v>-3546937460.211319</v>
+        <v>70344000</v>
       </c>
       <c r="P2" t="n">
-        <v>-4051720000</v>
+        <v>169707000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2039722000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>5088208000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5088208000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.7963</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.7963</v>
-      </c>
+        <v>2545162000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-4051720000</v>
+        <v>61014000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-108693000</v>
       </c>
       <c r="X2" t="n">
-        <v>-4051720000</v>
+        <v>169707000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-4051720000</v>
+        <v>169707000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3233000</v>
+        <v>-35711000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-4054953000</v>
+        <v>205418000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-4054953000</v>
+        <v>205418000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-786160000</v>
+        <v>178277000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4841113000</v>
+        <v>383695000</v>
       </c>
       <c r="AF2" t="n">
-        <v>414000</v>
+        <v>1769000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-592643000</v>
+        <v>8065000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-14766000</v>
+        <v>76000</v>
       </c>
       <c r="AI2" t="n">
-        <v>607409000</v>
+        <v>-8141000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-402980000</v>
+        <v>-174671000</v>
       </c>
       <c r="AK2" t="n">
-        <v>403554000</v>
+        <v>178165000</v>
       </c>
       <c r="AL2" t="n">
-        <v>574000</v>
+        <v>3494000</v>
       </c>
       <c r="AM2" t="n">
-        <v>38398000</v>
+        <v>382392000</v>
       </c>
       <c r="AN2" t="n">
-        <v>98073000</v>
+        <v>432077000</v>
       </c>
       <c r="AO2" t="n">
-        <v>32071000</v>
+        <v>34189000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1217000</v>
+        <v>2172000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1217000</v>
+        <v>2172000</v>
       </c>
       <c r="AR2" t="n">
-        <v>28907000</v>
+        <v>248490000</v>
       </c>
       <c r="AS2" t="n">
-        <v>13267000</v>
+        <v>137908000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15640000</v>
+        <v>110582000</v>
       </c>
       <c r="AU2" t="n">
-        <v>136471000</v>
+        <v>814469000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1941649000</v>
+        <v>2113085000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2078120000</v>
+        <v>2927554000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2078120000</v>
+        <v>2927554000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-42854568.181864</v>
+        <v>-75215750</v>
       </c>
       <c r="C3" t="n">
-        <v>0.147635</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-65442000</v>
+        <v>596962000</v>
       </c>
       <c r="E3" t="n">
-        <v>-290273000</v>
+        <v>-300863000</v>
       </c>
       <c r="F3" t="n">
-        <v>-290273000</v>
+        <v>-300863000</v>
       </c>
       <c r="G3" t="n">
-        <v>-464567000</v>
+        <v>42103000</v>
       </c>
       <c r="H3" t="n">
-        <v>9269000</v>
+        <v>5908000</v>
       </c>
       <c r="I3" t="n">
-        <v>2792884000</v>
+        <v>2491971000</v>
       </c>
       <c r="J3" t="n">
-        <v>-355715000</v>
+        <v>296099000</v>
       </c>
       <c r="K3" t="n">
-        <v>-364984000</v>
+        <v>290191000</v>
       </c>
       <c r="L3" t="n">
-        <v>-128389000</v>
+        <v>-114721000</v>
       </c>
       <c r="M3" t="n">
-        <v>130595000</v>
+        <v>117778000</v>
       </c>
       <c r="N3" t="n">
-        <v>2206000</v>
+        <v>3057000</v>
       </c>
       <c r="O3" t="n">
-        <v>-217148568.181864</v>
+        <v>267750250</v>
       </c>
       <c r="P3" t="n">
-        <v>-464567000</v>
+        <v>42103000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2946134000</v>
+        <v>2818627000</v>
       </c>
       <c r="R3" t="n">
-        <v>5088208000</v>
+        <v>6301800000</v>
       </c>
       <c r="S3" t="n">
         <v>5088208000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.0016</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="V3" t="n">
-        <v>-464567000</v>
+        <v>10025000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-32078000</v>
       </c>
       <c r="X3" t="n">
-        <v>-464567000</v>
+        <v>42103000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-464567000</v>
+        <v>42103000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-42153000</v>
+        <v>27827000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-422414000</v>
+        <v>14276000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-422414000</v>
+        <v>14276000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-73165000</v>
+        <v>158137000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-495579000</v>
+        <v>172413000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1104000</v>
+        <v>3133000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-296593000</v>
+        <v>-402293000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1857000</v>
+        <v>402293000</v>
       </c>
       <c r="AI3" t="n">
-        <v>298450000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-128389000</v>
+        <v>-114721000</v>
       </c>
       <c r="AK3" t="n">
-        <v>130595000</v>
+        <v>117778000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2206000</v>
+        <v>3057000</v>
       </c>
       <c r="AM3" t="n">
-        <v>356621000</v>
+        <v>630341000</v>
       </c>
       <c r="AN3" t="n">
-        <v>153250000</v>
+        <v>326656000</v>
       </c>
       <c r="AO3" t="n">
-        <v>26647000</v>
+        <v>30201000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7078000</v>
+        <v>1351000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7078000</v>
+        <v>1351000</v>
       </c>
       <c r="AR3" t="n">
-        <v>63464000</v>
+        <v>208360000</v>
       </c>
       <c r="AS3" t="n">
-        <v>39973000</v>
+        <v>145364000</v>
       </c>
       <c r="AT3" t="n">
-        <v>23491000</v>
+        <v>62996000</v>
       </c>
       <c r="AU3" t="n">
-        <v>509871000</v>
+        <v>956997000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2792884000</v>
+        <v>2491971000</v>
       </c>
       <c r="AW3" t="n">
-        <v>3302755000</v>
+        <v>3448968000</v>
       </c>
       <c r="AX3" t="n">
-        <v>3302755000</v>
+        <v>3448968000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-49642395</v>
+        <v>-42854568.181864</v>
       </c>
       <c r="C4" t="n">
-        <v>0.165</v>
+        <v>0.147635</v>
       </c>
       <c r="D4" t="n">
-        <v>596962000</v>
+        <v>-65442000</v>
       </c>
       <c r="E4" t="n">
-        <v>-300863000</v>
+        <v>-290273000</v>
       </c>
       <c r="F4" t="n">
-        <v>-300863000</v>
+        <v>-290273000</v>
       </c>
       <c r="G4" t="n">
-        <v>42103000</v>
+        <v>-464567000</v>
       </c>
       <c r="H4" t="n">
-        <v>5908000</v>
+        <v>9269000</v>
       </c>
       <c r="I4" t="n">
-        <v>2491971000</v>
+        <v>2792884000</v>
       </c>
       <c r="J4" t="n">
-        <v>296099000</v>
+        <v>-355715000</v>
       </c>
       <c r="K4" t="n">
-        <v>290191000</v>
+        <v>-364984000</v>
       </c>
       <c r="L4" t="n">
-        <v>-114721000</v>
+        <v>-128389000</v>
       </c>
       <c r="M4" t="n">
-        <v>117778000</v>
+        <v>130595000</v>
       </c>
       <c r="N4" t="n">
-        <v>3057000</v>
+        <v>2206000</v>
       </c>
       <c r="O4" t="n">
-        <v>293323605</v>
+        <v>-217148568.181864</v>
       </c>
       <c r="P4" t="n">
-        <v>42103000</v>
+        <v>-464567000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2818627000</v>
+        <v>2946134000</v>
       </c>
       <c r="R4" t="n">
-        <v>6301800000</v>
+        <v>5088208000</v>
       </c>
       <c r="S4" t="n">
         <v>5088208000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0016</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0083</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>10025000</v>
+        <v>-464567000</v>
       </c>
       <c r="W4" t="n">
-        <v>-32078000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42103000</v>
+        <v>-464567000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>42103000</v>
+        <v>-464567000</v>
       </c>
       <c r="AA4" t="n">
-        <v>27827000</v>
+        <v>-42153000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14276000</v>
+        <v>-422414000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14276000</v>
+        <v>-422414000</v>
       </c>
       <c r="AD4" t="n">
-        <v>158137000</v>
+        <v>-73165000</v>
       </c>
       <c r="AE4" t="n">
-        <v>172413000</v>
+        <v>-495579000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3133000</v>
+        <v>1104000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-402293000</v>
+        <v>-296593000</v>
       </c>
       <c r="AH4" t="n">
-        <v>402293000</v>
+        <v>-1857000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>298450000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-114721000</v>
+        <v>-128389000</v>
       </c>
       <c r="AK4" t="n">
-        <v>117778000</v>
+        <v>130595000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3057000</v>
+        <v>2206000</v>
       </c>
       <c r="AM4" t="n">
-        <v>630341000</v>
+        <v>356621000</v>
       </c>
       <c r="AN4" t="n">
-        <v>326656000</v>
+        <v>153250000</v>
       </c>
       <c r="AO4" t="n">
-        <v>30201000</v>
+        <v>26647000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1351000</v>
+        <v>7078000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1351000</v>
+        <v>7078000</v>
       </c>
       <c r="AR4" t="n">
-        <v>208360000</v>
+        <v>63464000</v>
       </c>
       <c r="AS4" t="n">
-        <v>145364000</v>
+        <v>39973000</v>
       </c>
       <c r="AT4" t="n">
-        <v>62996000</v>
+        <v>23491000</v>
       </c>
       <c r="AU4" t="n">
-        <v>956997000</v>
+        <v>509871000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2491971000</v>
+        <v>2792884000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3448968000</v>
+        <v>3302755000</v>
       </c>
       <c r="AX4" t="n">
-        <v>3448968000</v>
+        <v>3302755000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>21859860</v>
+        <v>-97865460.211319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.162392</v>
       </c>
       <c r="D5" t="n">
-        <v>449874000</v>
+        <v>-3833694000</v>
       </c>
       <c r="E5" t="n">
-        <v>132484000</v>
+        <v>-602648000</v>
       </c>
       <c r="F5" t="n">
-        <v>132484000</v>
+        <v>-602648000</v>
       </c>
       <c r="G5" t="n">
-        <v>169707000</v>
+        <v>-4051720000</v>
       </c>
       <c r="H5" t="n">
-        <v>20498000</v>
+        <v>1217000</v>
       </c>
       <c r="I5" t="n">
-        <v>2113085000</v>
+        <v>1941649000</v>
       </c>
       <c r="J5" t="n">
-        <v>582358000</v>
+        <v>-4436342000</v>
       </c>
       <c r="K5" t="n">
-        <v>561860000</v>
+        <v>-4437559000</v>
       </c>
       <c r="L5" t="n">
-        <v>-174671000</v>
+        <v>-402980000</v>
       </c>
       <c r="M5" t="n">
-        <v>178165000</v>
+        <v>403554000</v>
       </c>
       <c r="N5" t="n">
-        <v>3494000</v>
+        <v>574000</v>
       </c>
       <c r="O5" t="n">
-        <v>59082860</v>
+        <v>-3546937460.211319</v>
       </c>
       <c r="P5" t="n">
-        <v>169707000</v>
+        <v>-4051720000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2545162000</v>
+        <v>2039722000</v>
       </c>
       <c r="R5" t="n">
-        <v>6323670000</v>
+        <v>5088208000</v>
       </c>
       <c r="S5" t="n">
-        <v>5087441000</v>
+        <v>5088208000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.7963</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0334</v>
+        <v>-0.7963</v>
       </c>
       <c r="V5" t="n">
-        <v>61014000</v>
+        <v>-4051720000</v>
       </c>
       <c r="W5" t="n">
-        <v>-108693000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>169707000</v>
+        <v>-4051720000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>169707000</v>
+        <v>-4051720000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-35711000</v>
+        <v>3233000</v>
       </c>
       <c r="AB5" t="n">
-        <v>205418000</v>
+        <v>-4054953000</v>
       </c>
       <c r="AC5" t="n">
-        <v>205418000</v>
+        <v>-4054953000</v>
       </c>
       <c r="AD5" t="n">
-        <v>178277000</v>
+        <v>-786160000</v>
       </c>
       <c r="AE5" t="n">
-        <v>383695000</v>
+        <v>-4841113000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1769000</v>
+        <v>414000</v>
       </c>
       <c r="AG5" t="n">
-        <v>8065000</v>
+        <v>-592643000</v>
       </c>
       <c r="AH5" t="n">
-        <v>76000</v>
+        <v>-14766000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-8141000</v>
+        <v>607409000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-174671000</v>
+        <v>-402980000</v>
       </c>
       <c r="AK5" t="n">
-        <v>178165000</v>
+        <v>403554000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3494000</v>
+        <v>574000</v>
       </c>
       <c r="AM5" t="n">
-        <v>382392000</v>
+        <v>38398000</v>
       </c>
       <c r="AN5" t="n">
-        <v>432077000</v>
+        <v>98073000</v>
       </c>
       <c r="AO5" t="n">
-        <v>34189000</v>
+        <v>32071000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2172000</v>
+        <v>1217000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2172000</v>
+        <v>1217000</v>
       </c>
       <c r="AR5" t="n">
-        <v>248490000</v>
+        <v>28907000</v>
       </c>
       <c r="AS5" t="n">
-        <v>137908000</v>
+        <v>13267000</v>
       </c>
       <c r="AT5" t="n">
-        <v>110582000</v>
+        <v>15640000</v>
       </c>
       <c r="AU5" t="n">
-        <v>814469000</v>
+        <v>136471000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2113085000</v>
+        <v>1941649000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2927554000</v>
+        <v>2078120000</v>
       </c>
       <c r="AX5" t="n">
-        <v>2927554000</v>
-      </c>
+        <v>2078120000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>5088208000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5088208000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1065</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.1065</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1606,7 +1660,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>5088207546</v>
@@ -1615,42 +1669,46 @@
         <v>5088207546</v>
       </c>
       <c r="D2" t="n">
-        <v>6641176000</v>
+        <v>8412708000</v>
       </c>
       <c r="E2" t="n">
-        <v>6741591000</v>
+        <v>9005562000</v>
       </c>
       <c r="F2" t="n">
-        <v>331627000</v>
+        <v>4836052000</v>
       </c>
       <c r="G2" t="n">
-        <v>-5083910000</v>
+        <v>3564876000</v>
       </c>
       <c r="H2" t="n">
-        <v>331627000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>4836052000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="n">
-        <v>331627000</v>
+        <v>4836052000</v>
       </c>
       <c r="K2" t="n">
-        <v>331627000</v>
+        <v>12043044000</v>
       </c>
       <c r="L2" t="n">
-        <v>545469000</v>
+        <v>5105661000</v>
       </c>
       <c r="M2" t="n">
-        <v>213842000</v>
+        <v>269609000</v>
       </c>
       <c r="N2" t="n">
-        <v>331627000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>4836052000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12036000</v>
+      </c>
       <c r="P2" t="n">
         <v>1008997000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1286267000</v>
+        <v>3178682000</v>
       </c>
       <c r="R2" t="n">
         <v>833698000</v>
@@ -1662,124 +1720,132 @@
         <v>42890000</v>
       </c>
       <c r="U2" t="n">
-        <v>16312451000</v>
+        <v>24883037000</v>
       </c>
       <c r="V2" t="n">
-        <v>436572000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>86883000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>9142434000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>102071000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>443750000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>349689000</v>
+        <v>1389621000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>7206992000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>7206992000</v>
       </c>
       <c r="AD2" t="n">
-        <v>15875879000</v>
+        <v>15740603000</v>
       </c>
       <c r="AE2" t="n">
-        <v>6741591000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>1798570000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
       <c r="AG2" t="n">
-        <v>6741591000</v>
+        <v>1798570000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3621233000</v>
+        <v>2933374000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1920605000</v>
+        <v>1552601000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>778950000</v>
+        <v>502845000</v>
       </c>
       <c r="AK2" t="n">
-        <v>921678000</v>
+        <v>877928000</v>
       </c>
       <c r="AL2" t="n">
-        <v>16857920000</v>
+        <v>29988698000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6065951000</v>
+        <v>10683219000</v>
       </c>
       <c r="AN2" t="n">
-        <v>12104000</v>
+        <v>56373000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6005500000</v>
+        <v>10564740000</v>
       </c>
       <c r="AP2" t="n">
-        <v>48347000</v>
+        <v>62106000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-48417000</v>
+        <v>-52346000</v>
       </c>
       <c r="AR2" t="n">
-        <v>96764000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>114452000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>62106000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>30041000</v>
+        <v>41158000</v>
       </c>
       <c r="AU2" t="n">
-        <v>66723000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>73294000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>10791969000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>19305479000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>105689000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>63840000</v>
+        <v>121063000</v>
       </c>
       <c r="BA2" t="n">
-        <v>90101000</v>
+        <v>509164000</v>
       </c>
       <c r="BB2" t="n">
-        <v>780238000</v>
+        <v>1070860000</v>
       </c>
       <c r="BC2" t="n">
-        <v>9150262000</v>
+        <v>15993608000</v>
       </c>
       <c r="BD2" t="n">
-        <v>9150262000</v>
+        <v>15993608000</v>
       </c>
       <c r="BE2" t="n">
-        <v>474886000</v>
+        <v>997930000</v>
       </c>
       <c r="BF2" t="n">
-        <v>132227000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-7690000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>139917000</v>
-      </c>
+        <v>20000000</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>100415000</v>
+        <v>592854000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>100415000</v>
+        <v>592854000</v>
       </c>
       <c r="BK2" t="n">
-        <v>100415000</v>
+        <v>592854000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>5088208000</v>
@@ -1788,35 +1854,35 @@
         <v>5088208000</v>
       </c>
       <c r="D3" t="n">
-        <v>6897253000</v>
+        <v>7332590000</v>
       </c>
       <c r="E3" t="n">
-        <v>7045316000</v>
+        <v>7643537000</v>
       </c>
       <c r="F3" t="n">
-        <v>4392297000</v>
+        <v>4881630000</v>
       </c>
       <c r="G3" t="n">
-        <v>-1267232000</v>
+        <v>1542443000</v>
       </c>
       <c r="H3" t="n">
-        <v>4392297000</v>
+        <v>4881630000</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>4392297000</v>
+        <v>4881630000</v>
       </c>
       <c r="K3" t="n">
-        <v>7637206000</v>
+        <v>10591437000</v>
       </c>
       <c r="L3" t="n">
-        <v>4609372000</v>
+        <v>5074341000</v>
       </c>
       <c r="M3" t="n">
-        <v>217075000</v>
+        <v>192711000</v>
       </c>
       <c r="N3" t="n">
-        <v>4392297000</v>
+        <v>4881630000</v>
       </c>
       <c r="O3" t="n">
         <v>9235000</v>
@@ -1825,7 +1891,7 @@
         <v>1008997000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2756218000</v>
+        <v>3220785000</v>
       </c>
       <c r="R3" t="n">
         <v>833698000</v>
@@ -1837,124 +1903,122 @@
         <v>42890000</v>
       </c>
       <c r="U3" t="n">
-        <v>18797655000</v>
+        <v>21046996000</v>
       </c>
       <c r="V3" t="n">
-        <v>4562162000</v>
+        <v>7334677000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>6179000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>223750000</v>
+      </c>
       <c r="Z3" t="n">
-        <v>1317253000</v>
+        <v>1394941000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3244909000</v>
+        <v>5709807000</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>3244909000</v>
+        <v>5709807000</v>
       </c>
       <c r="AD3" t="n">
-        <v>14235493000</v>
+        <v>13712319000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3800407000</v>
+        <v>1933730000</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>3800407000</v>
+        <v>1933730000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3567132000</v>
+        <v>2173037000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1983071000</v>
+        <v>818295000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>728979000</v>
+        <v>592952000</v>
       </c>
       <c r="AK3" t="n">
-        <v>855082000</v>
+        <v>761790000</v>
       </c>
       <c r="AL3" t="n">
-        <v>23407027000</v>
+        <v>26121337000</v>
       </c>
       <c r="AM3" t="n">
-        <v>10438766000</v>
+        <v>10866575000</v>
       </c>
       <c r="AN3" t="n">
-        <v>156514000</v>
+        <v>74601000</v>
       </c>
       <c r="AO3" t="n">
-        <v>10233800000</v>
+        <v>10734280000</v>
       </c>
       <c r="AP3" t="n">
-        <v>48452000</v>
+        <v>57694000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-53682000</v>
+        <v>-45186000</v>
       </c>
       <c r="AR3" t="n">
-        <v>102134000</v>
+        <v>102880000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>33552000</v>
+        <v>34390000</v>
       </c>
       <c r="AU3" t="n">
-        <v>68582000</v>
+        <v>68490000</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>12968261000</v>
+        <v>15254762000</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>64228000</v>
+        <v>76682000</v>
       </c>
       <c r="BA3" t="n">
-        <v>250704000</v>
+        <v>487926000</v>
       </c>
       <c r="BB3" t="n">
-        <v>870930000</v>
+        <v>880141000</v>
       </c>
       <c r="BC3" t="n">
-        <v>11049745000</v>
+        <v>12971557000</v>
       </c>
       <c r="BD3" t="n">
-        <v>11049745000</v>
+        <v>12971557000</v>
       </c>
       <c r="BE3" t="n">
-        <v>489160000</v>
+        <v>480994000</v>
       </c>
       <c r="BF3" t="n">
-        <v>95431000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>95431000</v>
-      </c>
+        <v>46515000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>148063000</v>
+        <v>310947000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>148063000</v>
+        <v>310947000</v>
       </c>
       <c r="BK3" t="n">
-        <v>148063000</v>
+        <v>310947000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>5088208000</v>
@@ -1963,35 +2027,35 @@
         <v>5088208000</v>
       </c>
       <c r="D4" t="n">
-        <v>7332590000</v>
+        <v>6897253000</v>
       </c>
       <c r="E4" t="n">
-        <v>7643537000</v>
+        <v>7045316000</v>
       </c>
       <c r="F4" t="n">
-        <v>4881630000</v>
+        <v>4392297000</v>
       </c>
       <c r="G4" t="n">
-        <v>1542443000</v>
+        <v>-1267232000</v>
       </c>
       <c r="H4" t="n">
-        <v>4881630000</v>
+        <v>4392297000</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>4881630000</v>
+        <v>4392297000</v>
       </c>
       <c r="K4" t="n">
-        <v>10591437000</v>
+        <v>7637206000</v>
       </c>
       <c r="L4" t="n">
-        <v>5074341000</v>
+        <v>4609372000</v>
       </c>
       <c r="M4" t="n">
-        <v>192711000</v>
+        <v>217075000</v>
       </c>
       <c r="N4" t="n">
-        <v>4881630000</v>
+        <v>4392297000</v>
       </c>
       <c r="O4" t="n">
         <v>9235000</v>
@@ -2000,7 +2064,7 @@
         <v>1008997000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3220785000</v>
+        <v>2756218000</v>
       </c>
       <c r="R4" t="n">
         <v>833698000</v>
@@ -2012,122 +2076,124 @@
         <v>42890000</v>
       </c>
       <c r="U4" t="n">
-        <v>21046996000</v>
+        <v>18797655000</v>
       </c>
       <c r="V4" t="n">
-        <v>7334677000</v>
+        <v>4562162000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>6179000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>223750000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>1394941000</v>
+        <v>1317253000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5709807000</v>
+        <v>3244909000</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>5709807000</v>
+        <v>3244909000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13712319000</v>
+        <v>14235493000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1933730000</v>
+        <v>3800407000</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>1933730000</v>
+        <v>3800407000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2173037000</v>
+        <v>3567132000</v>
       </c>
       <c r="AI4" t="n">
-        <v>818295000</v>
+        <v>1983071000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>592952000</v>
+        <v>728979000</v>
       </c>
       <c r="AK4" t="n">
-        <v>761790000</v>
+        <v>855082000</v>
       </c>
       <c r="AL4" t="n">
-        <v>26121337000</v>
+        <v>23407027000</v>
       </c>
       <c r="AM4" t="n">
-        <v>10866575000</v>
+        <v>10438766000</v>
       </c>
       <c r="AN4" t="n">
-        <v>74601000</v>
+        <v>156514000</v>
       </c>
       <c r="AO4" t="n">
-        <v>10734280000</v>
+        <v>10233800000</v>
       </c>
       <c r="AP4" t="n">
-        <v>57694000</v>
+        <v>48452000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-45186000</v>
+        <v>-53682000</v>
       </c>
       <c r="AR4" t="n">
-        <v>102880000</v>
+        <v>102134000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>34390000</v>
+        <v>33552000</v>
       </c>
       <c r="AU4" t="n">
-        <v>68490000</v>
+        <v>68582000</v>
       </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>15254762000</v>
+        <v>12968261000</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>76682000</v>
+        <v>64228000</v>
       </c>
       <c r="BA4" t="n">
-        <v>487926000</v>
+        <v>250704000</v>
       </c>
       <c r="BB4" t="n">
-        <v>880141000</v>
+        <v>870930000</v>
       </c>
       <c r="BC4" t="n">
-        <v>12971557000</v>
+        <v>11049745000</v>
       </c>
       <c r="BD4" t="n">
-        <v>12971557000</v>
+        <v>11049745000</v>
       </c>
       <c r="BE4" t="n">
-        <v>480994000</v>
+        <v>489160000</v>
       </c>
       <c r="BF4" t="n">
-        <v>46515000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+        <v>95431000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>95431000</v>
+      </c>
       <c r="BI4" t="n">
-        <v>310947000</v>
+        <v>148063000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>310947000</v>
+        <v>148063000</v>
       </c>
       <c r="BK4" t="n">
-        <v>310947000</v>
+        <v>148063000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>5088207546</v>
@@ -2136,46 +2202,42 @@
         <v>5088207546</v>
       </c>
       <c r="D5" t="n">
-        <v>8412708000</v>
+        <v>6641176000</v>
       </c>
       <c r="E5" t="n">
-        <v>9005562000</v>
+        <v>6741591000</v>
       </c>
       <c r="F5" t="n">
-        <v>4836052000</v>
+        <v>331627000</v>
       </c>
       <c r="G5" t="n">
-        <v>3564876000</v>
+        <v>-5083910000</v>
       </c>
       <c r="H5" t="n">
-        <v>4836052000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+        <v>331627000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>4836052000</v>
+        <v>331627000</v>
       </c>
       <c r="K5" t="n">
-        <v>12043044000</v>
+        <v>331627000</v>
       </c>
       <c r="L5" t="n">
-        <v>5105661000</v>
+        <v>545469000</v>
       </c>
       <c r="M5" t="n">
-        <v>269609000</v>
+        <v>213842000</v>
       </c>
       <c r="N5" t="n">
-        <v>4836052000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>12036000</v>
-      </c>
+        <v>331627000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>1008997000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3178682000</v>
+        <v>-1286267000</v>
       </c>
       <c r="R5" t="n">
         <v>833698000</v>
@@ -2187,127 +2249,119 @@
         <v>42890000</v>
       </c>
       <c r="U5" t="n">
-        <v>24883037000</v>
+        <v>16312451000</v>
       </c>
       <c r="V5" t="n">
-        <v>9142434000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>102071000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>443750000</v>
-      </c>
+        <v>436572000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>86883000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>1389621000</v>
+        <v>349689000</v>
       </c>
       <c r="AA5" t="n">
-        <v>7206992000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>7206992000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>15740603000</v>
+        <v>15875879000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1798570000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
+        <v>6741591000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>1798570000</v>
+        <v>6741591000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2933374000</v>
+        <v>3621233000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1552601000</v>
+        <v>1920605000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502845000</v>
+        <v>778950000</v>
       </c>
       <c r="AK5" t="n">
-        <v>877928000</v>
+        <v>921678000</v>
       </c>
       <c r="AL5" t="n">
-        <v>29988698000</v>
+        <v>16857920000</v>
       </c>
       <c r="AM5" t="n">
-        <v>10683219000</v>
+        <v>6065951000</v>
       </c>
       <c r="AN5" t="n">
-        <v>56373000</v>
+        <v>12104000</v>
       </c>
       <c r="AO5" t="n">
-        <v>10564740000</v>
+        <v>6005500000</v>
       </c>
       <c r="AP5" t="n">
-        <v>62106000</v>
+        <v>48347000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-52346000</v>
+        <v>-48417000</v>
       </c>
       <c r="AR5" t="n">
-        <v>114452000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>62106000</v>
-      </c>
+        <v>96764000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>41158000</v>
+        <v>30041000</v>
       </c>
       <c r="AU5" t="n">
-        <v>73294000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
+        <v>66723000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>19305479000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>105689000</v>
-      </c>
+        <v>10791969000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>121063000</v>
+        <v>63840000</v>
       </c>
       <c r="BA5" t="n">
-        <v>509164000</v>
+        <v>90101000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1070860000</v>
+        <v>780238000</v>
       </c>
       <c r="BC5" t="n">
-        <v>15993608000</v>
+        <v>9150262000</v>
       </c>
       <c r="BD5" t="n">
-        <v>15993608000</v>
+        <v>9150262000</v>
       </c>
       <c r="BE5" t="n">
-        <v>997930000</v>
+        <v>474886000</v>
       </c>
       <c r="BF5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+        <v>132227000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-7690000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>139917000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>592854000</v>
+        <v>100415000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>592854000</v>
+        <v>100415000</v>
       </c>
       <c r="BK5" t="n">
-        <v>592854000</v>
+        <v>100415000</v>
       </c>
     </row>
   </sheetData>
@@ -2578,576 +2632,576 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>353416000</v>
+        <v>1449078000</v>
       </c>
       <c r="C2" t="n">
-        <v>-54988000</v>
+        <v>-4400733000</v>
       </c>
       <c r="D2" t="n">
-        <v>71533000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>4176000000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>234000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-1031000</v>
+        <v>-3647000</v>
       </c>
       <c r="G2" t="n">
-        <v>100415000</v>
+        <v>592854000</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>148063000</v>
+        <v>838036000</v>
       </c>
       <c r="J2" t="n">
-        <v>-8950000</v>
+        <v>-6699000</v>
       </c>
       <c r="K2" t="n">
-        <v>-38698000</v>
+        <v>-238483000</v>
       </c>
       <c r="L2" t="n">
-        <v>-366903000</v>
+        <v>-444234000</v>
       </c>
       <c r="M2" t="n">
-        <v>20059000</v>
+        <v>-179384000</v>
       </c>
       <c r="N2" t="n">
-        <v>-403507000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>-39987000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>234000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>234000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>16545000</v>
+        <v>-224733000</v>
       </c>
       <c r="R2" t="n">
-        <v>16545000</v>
+        <v>-224733000</v>
       </c>
       <c r="S2" t="n">
-        <v>-54988000</v>
+        <v>-4400733000</v>
       </c>
       <c r="T2" t="n">
-        <v>71533000</v>
+        <v>4176000000</v>
       </c>
       <c r="U2" t="n">
-        <v>-26242000</v>
+        <v>-1246974000</v>
       </c>
       <c r="V2" t="n">
-        <v>160603000</v>
+        <v>-307594000</v>
       </c>
       <c r="W2" t="n">
-        <v>574000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>3494000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2643000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2643000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-238301000</v>
+        <v>-714092000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4063000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-238301000</v>
+        <v>-718155000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-59000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-1031000</v>
+        <v>-3559000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1031000</v>
+        <v>-3647000</v>
       </c>
       <c r="AI2" t="n">
-        <v>354447000</v>
+        <v>1452725000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-5058000</v>
+        <v>-135372000</v>
       </c>
       <c r="AK2" t="n">
-        <v>321259000</v>
+        <v>1183271000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1476127000</v>
+        <v>2563187000</v>
       </c>
       <c r="AM2" t="n">
-        <v>512428000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>-367584000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-105689000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>1306930000</v>
+        <v>-845889000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-21972000</v>
+        <v>-60754000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>402980000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>174585000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>1217000</v>
+        <v>20498000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1217000</v>
+        <v>20498000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3813779000</v>
+        <v>-133681000</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-32292000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-27000</v>
+        <v>162000</v>
       </c>
       <c r="AX2" t="n">
-        <v>54001000</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>-4841113000</v>
+        <v>383695000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-10265000</v>
+        <v>1120450000</v>
       </c>
       <c r="C3" t="n">
-        <v>-799056000</v>
+        <v>-1672712000</v>
       </c>
       <c r="D3" t="n">
-        <v>137696000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>1015830000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-229000</v>
+        <v>-1073000</v>
       </c>
       <c r="G3" t="n">
-        <v>148063000</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>310947000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1000</v>
+      </c>
       <c r="I3" t="n">
-        <v>310947000</v>
+        <v>592854000</v>
       </c>
       <c r="J3" t="n">
-        <v>-24766000</v>
+        <v>6276000</v>
       </c>
       <c r="K3" t="n">
-        <v>-138118000</v>
+        <v>-288182000</v>
       </c>
       <c r="L3" t="n">
-        <v>-434395000</v>
+        <v>-1729984000</v>
       </c>
       <c r="M3" t="n">
-        <v>641835000</v>
+        <v>-672823000</v>
       </c>
       <c r="N3" t="n">
-        <v>-414870000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>-400279000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
-        <v>-661360000</v>
+        <v>-656882000</v>
       </c>
       <c r="R3" t="n">
-        <v>-661360000</v>
+        <v>-656882000</v>
       </c>
       <c r="S3" t="n">
-        <v>-799056000</v>
+        <v>-1672712000</v>
       </c>
       <c r="T3" t="n">
-        <v>137696000</v>
+        <v>1015830000</v>
       </c>
       <c r="U3" t="n">
-        <v>306313000</v>
+        <v>320279000</v>
       </c>
       <c r="V3" t="n">
-        <v>237223000</v>
+        <v>21238000</v>
       </c>
       <c r="W3" t="n">
-        <v>2206000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+        <v>3057000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>81057000</v>
+        <v>-118307000</v>
       </c>
       <c r="AA3" t="n">
-        <v>154354000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-73297000</v>
+        <v>-118307000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-35223000</v>
+        <v>66603000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>-66603000</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-39000</v>
+        <v>-1073000</v>
       </c>
       <c r="AG3" t="n">
-        <v>190000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-229000</v>
+        <v>-1073000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-10036000</v>
+        <v>1121523000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-18370000</v>
+        <v>-37241000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-374796000</v>
+        <v>519357000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-2197944000</v>
+        <v>-1284763000</v>
       </c>
       <c r="AM3" t="n">
-        <v>199796000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>693558000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
-        <v>1673434000</v>
+        <v>1310737000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-50082000</v>
+        <v>-200175000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>128389000</v>
+        <v>114721000</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>9269000</v>
+        <v>5908000</v>
       </c>
       <c r="AT3" t="n">
-        <v>9269000</v>
+        <v>5908000</v>
       </c>
       <c r="AU3" t="n">
-        <v>426522000</v>
+        <v>-94319000</v>
       </c>
       <c r="AV3" t="n">
-        <v>17936000</v>
+        <v>38391000</v>
       </c>
       <c r="AW3" t="n">
-        <v>417000</v>
+        <v>304000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-2274000</v>
+        <v>401989000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-495579000</v>
+        <v>172413000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1120450000</v>
+        <v>-10265000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1672712000</v>
+        <v>-799056000</v>
       </c>
       <c r="D4" t="n">
-        <v>1015830000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>137696000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-1073000</v>
+        <v>-229000</v>
       </c>
       <c r="G4" t="n">
+        <v>148063000</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>310947000</v>
       </c>
-      <c r="H4" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>592854000</v>
-      </c>
       <c r="J4" t="n">
-        <v>6276000</v>
+        <v>-24766000</v>
       </c>
       <c r="K4" t="n">
-        <v>-288182000</v>
+        <v>-138118000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1729984000</v>
+        <v>-434395000</v>
       </c>
       <c r="M4" t="n">
-        <v>-672823000</v>
+        <v>641835000</v>
       </c>
       <c r="N4" t="n">
-        <v>-400279000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+        <v>-414870000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-656882000</v>
+        <v>-661360000</v>
       </c>
       <c r="R4" t="n">
-        <v>-656882000</v>
+        <v>-661360000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1672712000</v>
+        <v>-799056000</v>
       </c>
       <c r="T4" t="n">
-        <v>1015830000</v>
+        <v>137696000</v>
       </c>
       <c r="U4" t="n">
-        <v>320279000</v>
+        <v>306313000</v>
       </c>
       <c r="V4" t="n">
-        <v>21238000</v>
+        <v>237223000</v>
       </c>
       <c r="W4" t="n">
-        <v>3057000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>2206000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-118307000</v>
+        <v>81057000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>154354000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-118307000</v>
+        <v>-73297000</v>
       </c>
       <c r="AC4" t="n">
-        <v>66603000</v>
+        <v>-35223000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>-66603000</v>
-      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-1073000</v>
+        <v>-39000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1073000</v>
+        <v>-229000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1121523000</v>
+        <v>-10036000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-37241000</v>
+        <v>-18370000</v>
       </c>
       <c r="AK4" t="n">
-        <v>519357000</v>
+        <v>-374796000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1284763000</v>
+        <v>-2197944000</v>
       </c>
       <c r="AM4" t="n">
-        <v>693558000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+        <v>199796000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>1310737000</v>
+        <v>1673434000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-200175000</v>
+        <v>-50082000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>114721000</v>
+        <v>128389000</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>5908000</v>
+        <v>9269000</v>
       </c>
       <c r="AT4" t="n">
-        <v>5908000</v>
+        <v>9269000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-94319000</v>
+        <v>426522000</v>
       </c>
       <c r="AV4" t="n">
-        <v>38391000</v>
+        <v>17936000</v>
       </c>
       <c r="AW4" t="n">
-        <v>304000</v>
+        <v>417000</v>
       </c>
       <c r="AX4" t="n">
-        <v>401989000</v>
+        <v>-2274000</v>
       </c>
       <c r="AY4" t="n">
-        <v>172413000</v>
+        <v>-495579000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1449078000</v>
+        <v>353416000</v>
       </c>
       <c r="C5" t="n">
-        <v>-4400733000</v>
+        <v>-54988000</v>
       </c>
       <c r="D5" t="n">
-        <v>4176000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>234000</v>
-      </c>
+        <v>71533000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-3647000</v>
+        <v>-1031000</v>
       </c>
       <c r="G5" t="n">
-        <v>592854000</v>
+        <v>100415000</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>838036000</v>
+        <v>148063000</v>
       </c>
       <c r="J5" t="n">
-        <v>-6699000</v>
+        <v>-8950000</v>
       </c>
       <c r="K5" t="n">
-        <v>-238483000</v>
+        <v>-38698000</v>
       </c>
       <c r="L5" t="n">
-        <v>-444234000</v>
+        <v>-366903000</v>
       </c>
       <c r="M5" t="n">
-        <v>-179384000</v>
+        <v>20059000</v>
       </c>
       <c r="N5" t="n">
-        <v>-39987000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>234000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>234000</v>
-      </c>
+        <v>-403507000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-224733000</v>
+        <v>16545000</v>
       </c>
       <c r="R5" t="n">
-        <v>-224733000</v>
+        <v>16545000</v>
       </c>
       <c r="S5" t="n">
-        <v>-4400733000</v>
+        <v>-54988000</v>
       </c>
       <c r="T5" t="n">
-        <v>4176000000</v>
+        <v>71533000</v>
       </c>
       <c r="U5" t="n">
-        <v>-1246974000</v>
+        <v>-26242000</v>
       </c>
       <c r="V5" t="n">
-        <v>-307594000</v>
+        <v>160603000</v>
       </c>
       <c r="W5" t="n">
-        <v>3494000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2643000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2643000</v>
-      </c>
+        <v>574000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-714092000</v>
+        <v>-238301000</v>
       </c>
       <c r="AA5" t="n">
-        <v>4063000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-718155000</v>
+        <v>-238301000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>-59000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-3559000</v>
+        <v>-1031000</v>
       </c>
       <c r="AG5" t="n">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3647000</v>
+        <v>-1031000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1452725000</v>
+        <v>354447000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-135372000</v>
+        <v>-5058000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1183271000</v>
+        <v>321259000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2563187000</v>
+        <v>-1476127000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-367584000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-105689000</v>
-      </c>
+        <v>512428000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>-845889000</v>
+        <v>1306930000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-60754000</v>
+        <v>-21972000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>174585000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>402980000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>20498000</v>
+        <v>1217000</v>
       </c>
       <c r="AT5" t="n">
-        <v>20498000</v>
+        <v>1217000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-133681000</v>
+        <v>3813779000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-32292000</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>162000</v>
+        <v>-27000</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>54001000</v>
       </c>
       <c r="AY5" t="n">
-        <v>383695000</v>
+        <v>-4841113000</v>
       </c>
     </row>
   </sheetData>
@@ -3667,187 +3721,187 @@
       </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EH1" t="inlineStr">
@@ -3927,11 +3981,11 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jiadi  Guo', 'age': 66, 'title': 'Executive Chairman', 'yearBorn': 1959, 'fiscalYear': 2024, 'totalPay': 752792, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chao  Wang', 'age': 47, 'title': 'Executive Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 656666, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Shing  Chan HKICPA', 'age': 46, 'title': 'Chief Financial Officer', 'yearBorn': 1979, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Kong  Poon', 'age': 54, 'title': 'Company Secretary', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jiadi  Guo', 'age': 66, 'title': 'Executive Chairman', 'yearBorn': 1959, 'fiscalYear': 2025, 'totalPay': 754027, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chao  Wang', 'age': 47, 'title': 'Executive Director', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 752868, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Shing  Chan HKICPA', 'age': 46, 'title': 'Chief Financial Officer', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Kong  Poon', 'age': 54, 'title': 'Company Secretary', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1735603200</v>
+        <v>1767139200</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -3978,7 +4032,7 @@
         <v>1.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.296</v>
+        <v>0.325</v>
       </c>
       <c r="AE2" t="n">
         <v>3433500</v>
@@ -4070,7 +4124,7 @@
         <v>5088207546</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.03937682</v>
+        <v>-0.0393808</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -4105,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BT2" t="n">
         <v>0.023791</v>
@@ -4212,142 +4266,142 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>-0.0020000003</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.013 - 0.015</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.0010000002</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.07692309</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>0.013 - 0.015</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.0009999992</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.06666662</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1756378740</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1756728000</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="DM2" t="inlineStr">
         <is>
           <t>China Sandi Holdings Limited</t>
         </is>
       </c>
-      <c r="CX2" t="n">
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1743407047</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_10360600</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>CHINA SANDI</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.3555032</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
         <v>-12.500002</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="EG2" t="n">
         <v>0.014</v>
       </c>
-      <c r="CZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>946949400000</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.0020000003</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>0.013 - 0.015</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.0010000002</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.07692309</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>0.013 - 0.015</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.0009999992</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.06666662</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1756378740</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1756728000</v>
-      </c>
-      <c r="DN2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.3555391</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>CHINA SANDI</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1743407047</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>finmb_10360600</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr"/>
